--- a/output/fwreq_prd.xlsx
+++ b/output/fwreq_prd.xlsx
@@ -491,12 +491,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Firmware Update – Enable Secure Boot for Platform Integrity</t>
+          <t>Firmware Update – Secure Boot Enablement</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Alex Kim</t>
+          <t>John Smith</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -506,22 +506,22 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Implement Secure Boot functionality in the firmware to ensure only signed and trusted code is executed during the boot process.</t>
+          <t>Implement Secure Boot functionality in the firmware to ensure only signed and trusted firmware images are executed during the boot process.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Prevents unauthorized or malicious code from running at boot, protecting platform integrity and reducing security risks.</t>
+          <t>Addresses critical security requirements by preventing unauthorized or malicious firmware from running, aligning with industry standards.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Enhances device security, meets enterprise compliance requirements, and increases customer trust in platform reliability.</t>
+          <t>Reduces risk of firmware attacks, increases customer trust, and meets compliance requirements for enterprise deployments.</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Users and IT administrators should have confidence that the device firmware is protected against tampering and unauthorized changes.</t>
+          <t>End users and IT admins should have confidence that the device firmware is protected from tampering.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -531,12 +531,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Secure Boot enabled and verified on all production units.</t>
+          <t>Secure Boot enabled and verified on all production firmware images.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Zero unsigned code execution during boot; seamless user experience with no boot delays.</t>
+          <t>100% of shipped units have Secure Boot enabled by default.</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -551,7 +551,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Security Engineering; Platform Firmware Team; Compliance Team</t>
+          <t>Security Engineering; Platform Firmware Team</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -563,12 +563,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Power Management – Adaptive Sleep Mode Enhancement</t>
+          <t>Power Management – Sleep Mode Optimization</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Priya Desai</t>
+          <t>Emily Chen</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -578,22 +578,22 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Enhance firmware to support adaptive sleep mode, dynamically adjusting power states based on usage patterns to optimize battery life.</t>
+          <t>Optimize firmware sleep mode routines to reduce power consumption during idle states without impacting wake-up performance.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Improves competitive positioning by extending battery life and reducing energy consumption, addressing key customer pain points.</t>
+          <t>Improves energy efficiency, extends battery life, and supports sustainability goals for the Victoria program.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Longer device uptime, reduced energy costs, and improved sustainability metrics.</t>
+          <t>Lower operational costs for customers and improved device ratings for energy consumption.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Users should notice longer battery life without manual intervention or performance degradation.</t>
+          <t>Users should experience longer battery life and faster wake times from sleep mode.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -603,12 +603,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Adaptive sleep mode functional and validated under standard usage scenarios.</t>
+          <t>Sleep mode power consumption reduced by at least 10% compared to previous generation.</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Achieve at least 10% improvement in average battery life compared to baseline.</t>
+          <t>Achieve 15% reduction in sleep mode power consumption.</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -618,12 +618,12 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Power management firmware modules; Usage analytics integration</t>
+          <t>Power management IC; OS power policy alignment</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Platform Power Team; Firmware QA; Analytics Team</t>
+          <t>Platform Power Team; OS Integration</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -635,12 +635,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Firmware Logging – Unified Error Reporting Framework</t>
+          <t>Diagnostics Logging – Enhanced Error Reporting</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Jorge Martinez</t>
+          <t>Michael Lee</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -650,37 +650,37 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Develop a unified error reporting framework in firmware to standardize logging and error codes across all subsystems.</t>
+          <t>Enhance firmware logging to capture detailed error codes and system state information for improved troubleshooting.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Facilitates faster troubleshooting, reduces support costs, and improves field issue resolution rates.</t>
+          <t>Enables faster root cause analysis and reduces support costs by providing actionable diagnostic data.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Consistent error reporting enables efficient diagnostics and better customer support experiences.</t>
+          <t>Improved customer support experience and reduced time to resolution for firmware-related issues.</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Technicians and support staff can quickly identify and resolve issues using standardized error logs.</t>
+          <t>Support teams can quickly identify and resolve issues using comprehensive logs.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>All Victoria program firmware subsystems.</t>
+          <t>All Victoria program firmware releases.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Unified error codes implemented and documented for all major error conditions.</t>
+          <t>All critical errors must be logged with unique error codes and relevant system context.</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>100% subsystem coverage with standardized error reporting.</t>
+          <t>100% coverage of critical error scenarios in diagnostic logs.</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -690,12 +690,12 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Subsystem firmware teams; Logging infrastructure</t>
+          <t>Logging framework; Support tools integration</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Diagnostics Team; Customer Support; Firmware Architecture</t>
+          <t>Customer Support; Firmware QA</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">

--- a/output/fwreq_prd.xlsx
+++ b/output/fwreq_prd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N7"/>
+  <dimension ref="A1:N12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,12 +491,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Firmware Update – Secure Boot Enablement</t>
+          <t>Firmware Update – Add Secure Boot Support</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>John Smith</t>
+          <t>Alex Kim</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -511,32 +511,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Addresses critical security requirements by preventing unauthorized or malicious firmware from running, aligning with industry standards.</t>
+          <t>Addresses increasing security threats and aligns with industry standards for device integrity.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Reduces risk of firmware attacks, increases customer trust, and meets compliance requirements for enterprise deployments.</t>
+          <t>Reduces risk of unauthorized firmware execution, enhances customer trust, and meets compliance requirements.</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>End users and IT admins should have confidence that the device firmware is protected from tampering.</t>
+          <t>End users should not notice any change in boot experience unless an unauthorized firmware is detected.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Applies to all new platforms launching with the Victoria program; does not include retrofitting for legacy devices.</t>
+          <t>Applies to all new platforms launching in 2025 and any platforms receiving major firmware updates.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Secure Boot enabled and verified on all production firmware images.</t>
+          <t>Secure Boot enabled by default; blocks unsigned firmware.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>100% of shipped units have Secure Boot enabled by default.</t>
+          <t>Zero successful unauthorized firmware loads in validation and field.</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -546,7 +546,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Firmware signing infrastructure; Platform security module integration</t>
+          <t>Firmware signing infrastructure; Platform security module</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -563,52 +563,52 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Power Management – Sleep Mode Optimization</t>
+          <t>Thermal Management – Adaptive Fan Control Algorithm</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Emily Chen</t>
+          <t>Priya Desai</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Thermal</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Optimize firmware sleep mode routines to reduce power consumption during idle states without impacting wake-up performance.</t>
+          <t>Develop and integrate an adaptive fan control algorithm that dynamically adjusts fan speed based on real-time thermal sensor data.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Improves energy efficiency, extends battery life, and supports sustainability goals for the Victoria program.</t>
+          <t>Improves device reliability and user comfort by optimizing thermal performance and reducing noise.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lower operational costs for customers and improved device ratings for energy consumption.</t>
+          <t>Extends hardware lifespan, reduces RMA rates, and enhances user satisfaction through quieter operation.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Users should experience longer battery life and faster wake times from sleep mode.</t>
+          <t>Users should experience quieter fan operation without thermal throttling or overheating.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Victoria program platforms with battery-powered configurations.</t>
+          <t>All desktop and workstation platforms with multi-zone thermal sensors.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Sleep mode power consumption reduced by at least 10% compared to previous generation.</t>
+          <t>Fan speed dynamically adjusts to maintain CPU temperature below 80°C under typical workloads.</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Achieve 15% reduction in sleep mode power consumption.</t>
+          <t>Maintain CPU temperature below 75°C in 95% of use cases.</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -618,12 +618,12 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Power management IC; OS power policy alignment</t>
+          <t>Thermal sensors; Fan controller firmware</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Platform Power Team; OS Integration</t>
+          <t>Thermal Engineering; Hardware Validation</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -635,52 +635,52 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Diagnostics Logging – Enhanced Error Reporting</t>
+          <t>Firmware Logging – Enhanced Debug Trace</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Michael Lee</t>
+          <t>Samir Patel</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Diagnostics</t>
+          <t>Debug/Diagnostics</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Enhance firmware logging to capture detailed error codes and system state information for improved troubleshooting.</t>
+          <t>Expand firmware debug trace capabilities to include timestamped event logging and error categorization.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Enables faster root cause analysis and reduces support costs by providing actionable diagnostic data.</t>
+          <t>Facilitates faster root cause analysis and reduces time-to-resolution for field issues.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Improved customer support experience and reduced time to resolution for firmware-related issues.</t>
+          <t>Improves support efficiency and reduces engineering costs associated with issue triage.</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Support teams can quickly identify and resolve issues using comprehensive logs.</t>
+          <t>Support teams can retrieve detailed logs for troubleshooting without impacting device performance.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>All Victoria program firmware releases.</t>
+          <t>All platforms supporting debug UART or persistent storage for logs.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>All critical errors must be logged with unique error codes and relevant system context.</t>
+          <t>Timestamped logs for all critical firmware events.</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>100% coverage of critical error scenarios in diagnostic logs.</t>
+          <t>Categorize 100% of firmware errors with timestamps and event IDs.</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -690,12 +690,12 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Logging framework; Support tools integration</t>
+          <t>Debug UART; Persistent storage; Logging framework</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Customer Support; Firmware QA</t>
+          <t>Firmware QA; Customer Support</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -752,6 +752,142 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr"/>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr"/>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Firmware Update – Reduce Boot Time to Under 10 Seconds</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Alex Kim</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Reduce the device boot time so that the system is fully operational in under 10 seconds from power-on.</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Faster boot times improve user satisfaction and perceived product quality, supporting competitive positioning.</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Shorter wait times for users, improved first impression, and increased device usability in time-sensitive scenarios.</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Users should experience minimal delay from power-on to ready state.</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Firmware boot sequence optimization; hardware initialization routines.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Boot time ≤ 10 seconds</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Boot time ≤ 8 seconds</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Hardware initialization; firmware bootloader</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Firmware team; Hardware team</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/fwreq_prd.xlsx
+++ b/output/fwreq_prd.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Alex Kim</t>
+          <t>John Smith</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -511,32 +511,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Addresses increasing security threats and aligns with industry standards for device integrity.</t>
+          <t>Addresses critical security requirements for enterprise customers and compliance with industry standards.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Reduces risk of unauthorized firmware execution, enhances customer trust, and meets compliance requirements.</t>
+          <t>Reduces risk of unauthorized firmware execution, enhances device trustworthiness, and supports regulatory compliance.</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>End users should not notice any change in boot experience unless an unauthorized firmware is detected.</t>
+          <t>End users and IT admins should have confidence that devices are protected from malicious firmware at boot.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Applies to all new platforms launching in 2025 and any platforms receiving major firmware updates.</t>
+          <t>All new platforms launching in 2025; does not apply to legacy platforms.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Secure Boot enabled by default; blocks unsigned firmware.</t>
+          <t>Secure Boot enabled and verified on all supported platforms.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Zero successful unauthorized firmware loads in validation and field.</t>
+          <t>Zero unsigned firmware allowed to execute; seamless user experience during boot.</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -546,12 +546,12 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Firmware signing infrastructure; Platform security module</t>
+          <t>Platform hardware support for Secure Boot; signed firmware build pipeline.</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Security Engineering; Platform Firmware Team</t>
+          <t>Security Architecture Team; Platform Firmware Team</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -563,52 +563,52 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Thermal Management – Adaptive Fan Control Algorithm</t>
+          <t>Power Management – Deep Sleep Mode Enhancement</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Priya Desai</t>
+          <t>Priya Patel</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Thermal</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Develop and integrate an adaptive fan control algorithm that dynamically adjusts fan speed based on real-time thermal sensor data.</t>
+          <t>Enhance firmware to support a new deep sleep mode that reduces power consumption below 0.5W during idle states.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Improves device reliability and user comfort by optimizing thermal performance and reducing noise.</t>
+          <t>Improves energy efficiency and extends battery life, meeting sustainability goals.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Extends hardware lifespan, reduces RMA rates, and enhances user satisfaction through quieter operation.</t>
+          <t>Lower operational costs for customers and improved device ratings for energy efficiency.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Users should experience quieter fan operation without thermal throttling or overheating.</t>
+          <t>Users should not notice any delay when resuming from deep sleep mode.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>All desktop and workstation platforms with multi-zone thermal sensors.</t>
+          <t>Applies to all battery-powered Victoria platforms.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Fan speed dynamically adjusts to maintain CPU temperature below 80°C under typical workloads.</t>
+          <t>Idle power consumption ≤ 0.5W in deep sleep mode.</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Maintain CPU temperature below 75°C in 95% of use cases.</t>
+          <t>Achieve 0.3W or lower in deep sleep mode.</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -618,12 +618,12 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Thermal sensors; Fan controller firmware</t>
+          <t>Hardware support for low-power states; OS coordination for sleep transitions.</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Thermal Engineering; Hardware Validation</t>
+          <t>Power Architecture Team; Hardware Engineering</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -635,52 +635,52 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Firmware Logging – Enhanced Debug Trace</t>
+          <t>Firmware Logging – Remote Diagnostics Support</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Samir Patel</t>
+          <t>Alex Chen</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Debug/Diagnostics</t>
+          <t>Diagnostics</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Expand firmware debug trace capabilities to include timestamped event logging and error categorization.</t>
+          <t>Add remote diagnostics logging capability to firmware, enabling log retrieval over the network for support teams.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Facilitates faster root cause analysis and reduces time-to-resolution for field issues.</t>
+          <t>Reduces time to resolution for field issues and improves support efficiency.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Improves support efficiency and reduces engineering costs associated with issue triage.</t>
+          <t>Faster troubleshooting, reduced need for device returns, and improved customer satisfaction.</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Support teams can retrieve detailed logs for troubleshooting without impacting device performance.</t>
+          <t>Support teams can securely access logs without requiring physical access to the device.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>All platforms supporting debug UART or persistent storage for logs.</t>
+          <t>All Victoria platforms with network connectivity.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Timestamped logs for all critical firmware events.</t>
+          <t>Remote log retrieval functional and secure.</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Categorize 100% of firmware errors with timestamps and event IDs.</t>
+          <t>Logs available within 2 minutes of request; access restricted to authorized personnel.</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -690,12 +690,12 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Debug UART; Persistent storage; Logging framework</t>
+          <t>Network stack integration; secure authentication mechanisms.</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Firmware QA; Customer Support</t>
+          <t>Support Engineering; Firmware Team; IT Security</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -819,52 +819,52 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Firmware Update – Reduce Boot Time to Under 10 Seconds</t>
+          <t>Firmware Update Notification Enhancement</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Alex Kim</t>
+          <t>John Smith</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Update Experience</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Reduce the device boot time so that the system is fully operational in under 10 seconds from power-on.</t>
+          <t>Implement a user-facing notification system in firmware to alert users when a new firmware update is available.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Faster boot times improve user satisfaction and perceived product quality, supporting competitive positioning.</t>
+          <t>Ensures users are aware of critical firmware updates, leading to improved device security and performance.</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Shorter wait times for users, improved first impression, and increased device usability in time-sensitive scenarios.</t>
+          <t>Increases firmware update adoption rates and reduces support calls related to outdated firmware.</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Users should experience minimal delay from power-on to ready state.</t>
+          <t>Users should receive clear, actionable notifications about firmware updates directly on their device.</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Firmware boot sequence optimization; hardware initialization routines.</t>
+          <t>All devices supporting over-the-air firmware updates.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Boot time ≤ 10 seconds</t>
+          <t>Notification appears within 24 hours of update availability.</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Boot time ≤ 8 seconds</t>
+          <t>Notification appears within 1 hour of update availability.</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -874,12 +874,12 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Hardware initialization; firmware bootloader</t>
+          <t>OTA update infrastructure; device notification framework</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Firmware team; Hardware team</t>
+          <t>Firmware team; UX design; QA</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
